--- a/pixy2/pixy2.xlsx
+++ b/pixy2/pixy2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/likayauelwin/Documents/GitHub/2025-WRO-Future-Engineer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/likayauelwin/Documents/GitHub/2025-WRO-Future-Engineer/pixy2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C1C006-B70A-4040-B0BC-4F10D7A196FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67818932-DC4C-D940-912C-14FAF73BA676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-640" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{50C2FC8F-A61D-EA40-BD48-FD46821D1210}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="27960" windowHeight="18360" xr2:uid="{50C2FC8F-A61D-EA40-BD48-FD46821D1210}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1730,15 +1730,14 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="6"/>
+            <c:trendlineType val="power"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="8.9025074665838339E-2"/>
-                  <c:y val="9.412831279064518E-2"/>
+                  <c:x val="-0.12658739023782276"/>
+                  <c:y val="9.5925350579016563E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="#,##0.000000000" sourceLinked="0"/>
